--- a/data-source/COMPRATRANSFER.xlsx
+++ b/data-source/COMPRATRANSFER.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5b319cc1648f3add/Área de Trabalho/TRANSFER-ANALISE/data-source/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="22" documentId="14_{42D477D6-2A30-45A0-ABAB-3676C37B368B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{448DCE3B-4AFB-419D-9829-7635BAE0B21A}"/>
+  <xr:revisionPtr revIDLastSave="62" documentId="14_{42D477D6-2A30-45A0-ABAB-3676C37B368B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{176C7177-5918-4717-A480-C295F4F3D017}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="29">
   <si>
     <t>Núm.OC</t>
   </si>
@@ -118,6 +118,12 @@
   </si>
   <si>
     <t>TRANSFER 99-5-4 PARCIAL FILM - ROSE GOLD</t>
+  </si>
+  <si>
+    <t>TRANSFER 99-5-4 PARCIAL FOIL - GRAPHITE</t>
+  </si>
+  <si>
+    <t>TRANSFER 99-5-4 PARCIAL FOIL - ROSE GOLD</t>
   </si>
 </sst>
 </file>
@@ -158,7 +164,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
+        <fgColor theme="9" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -548,7 +554,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I22"/>
+  <dimension ref="A1:I24"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.33203125" bestFit="1" customWidth="1"/>
@@ -959,7 +965,7 @@
         <v>11</v>
       </c>
       <c r="G14" s="6">
-        <v>6000</v>
+        <v>6700</v>
       </c>
       <c r="H14" s="7">
         <v>12</v>
@@ -1198,6 +1204,64 @@
       </c>
       <c r="I22" s="7" t="s">
         <v>17</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A23" s="8">
+        <v>1840</v>
+      </c>
+      <c r="B23" s="3">
+        <v>162</v>
+      </c>
+      <c r="C23" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D23" s="5">
+        <v>46288</v>
+      </c>
+      <c r="E23" s="8">
+        <v>12517</v>
+      </c>
+      <c r="F23" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="G23" s="6">
+        <v>2000</v>
+      </c>
+      <c r="H23" s="7">
+        <v>12</v>
+      </c>
+      <c r="I23" s="7" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A24" s="8">
+        <v>1840</v>
+      </c>
+      <c r="B24" s="3">
+        <v>162</v>
+      </c>
+      <c r="C24" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D24" s="5">
+        <v>46288</v>
+      </c>
+      <c r="E24" s="8">
+        <v>12518</v>
+      </c>
+      <c r="F24" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="G24" s="6">
+        <v>2000</v>
+      </c>
+      <c r="H24" s="7">
+        <v>12</v>
+      </c>
+      <c r="I24" s="7" t="s">
+        <v>18</v>
       </c>
     </row>
   </sheetData>

--- a/data-source/COMPRATRANSFER.xlsx
+++ b/data-source/COMPRATRANSFER.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5b319cc1648f3add/Área de Trabalho/TRANSFER-ANALISE/data-source/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\impre\Downloads\TRANSFER-ANALISE-CORRIGIDO\data-source\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="62" documentId="14_{42D477D6-2A30-45A0-ABAB-3676C37B368B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{176C7177-5918-4717-A480-C295F4F3D017}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F0CEBF1E-428A-45CB-A3E8-FC1D812DEE91}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Plan1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Plan1!$A$1:$I$17</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Plan1!$A$1:$I$16</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">Plan1!$1:$1</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="29">
   <si>
     <t>Núm.OC</t>
   </si>
@@ -99,9 +99,6 @@
     <t>qtd_aberto</t>
   </si>
   <si>
-    <t>PROTECTION FILM</t>
-  </si>
-  <si>
     <t>PROTECTION FILM 35UM - AMERICA ASIA</t>
   </si>
   <si>
@@ -124,6 +121,9 @@
   </si>
   <si>
     <t>TRANSFER 99-5-4 PARCIAL FOIL - ROSE GOLD</t>
+  </si>
+  <si>
+    <t>PROTECTION</t>
   </si>
 </sst>
 </file>
@@ -150,7 +150,7 @@
       <name val="Calibri"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -165,6 +165,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="3" tint="0.89999084444715716"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -207,7 +213,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -217,6 +223,12 @@
     <xf numFmtId="165" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="166" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="49" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="14" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="165" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="166" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -554,7 +566,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I24"/>
+  <dimension ref="A1:I23"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.33203125" bestFit="1" customWidth="1"/>
@@ -598,443 +610,443 @@
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A2" s="3">
+      <c r="A2" s="9">
         <v>1565</v>
       </c>
-      <c r="B2" s="3">
-        <v>162</v>
-      </c>
-      <c r="C2" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="D2" s="5">
+      <c r="B2" s="9">
+        <v>162</v>
+      </c>
+      <c r="C2" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="D2" s="11">
         <v>46225</v>
       </c>
-      <c r="E2" s="3">
+      <c r="E2" s="9">
         <v>7484</v>
       </c>
-      <c r="F2" s="4" t="s">
+      <c r="F2" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="G2" s="6">
+      <c r="G2" s="12">
         <v>8800</v>
       </c>
-      <c r="H2" s="7">
-        <v>12</v>
-      </c>
-      <c r="I2" s="7" t="s">
+      <c r="H2" s="13">
+        <v>12</v>
+      </c>
+      <c r="I2" s="13" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A3" s="3">
+      <c r="A3" s="9">
         <v>1565</v>
       </c>
-      <c r="B3" s="3">
-        <v>162</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="D3" s="5">
+      <c r="B3" s="9">
+        <v>162</v>
+      </c>
+      <c r="C3" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="D3" s="11">
         <v>46225</v>
       </c>
-      <c r="E3" s="3">
+      <c r="E3" s="9">
         <v>7485</v>
       </c>
-      <c r="F3" s="4" t="s">
+      <c r="F3" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="G3" s="6">
+      <c r="G3" s="12">
         <v>6000</v>
       </c>
-      <c r="H3" s="7">
-        <v>12</v>
-      </c>
-      <c r="I3" s="7" t="s">
+      <c r="H3" s="13">
+        <v>12</v>
+      </c>
+      <c r="I3" s="13" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A4" s="3">
+      <c r="A4" s="9">
         <v>1565</v>
       </c>
-      <c r="B4" s="3">
-        <v>162</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="D4" s="5">
+      <c r="B4" s="9">
+        <v>162</v>
+      </c>
+      <c r="C4" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="D4" s="11">
         <v>46225</v>
       </c>
-      <c r="E4" s="3">
+      <c r="E4" s="9">
         <v>10090</v>
       </c>
-      <c r="F4" s="4" t="s">
+      <c r="F4" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="G4" s="6">
+      <c r="G4" s="12">
         <v>3200</v>
       </c>
-      <c r="H4" s="7">
-        <v>12</v>
-      </c>
-      <c r="I4" s="7" t="s">
+      <c r="H4" s="13">
+        <v>12</v>
+      </c>
+      <c r="I4" s="13" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A5" s="3">
+      <c r="A5" s="9">
         <v>1565</v>
       </c>
-      <c r="B5" s="3">
-        <v>162</v>
-      </c>
-      <c r="C5" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="D5" s="5">
+      <c r="B5" s="9">
+        <v>162</v>
+      </c>
+      <c r="C5" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="D5" s="11">
         <v>46225</v>
       </c>
-      <c r="E5" s="3">
+      <c r="E5" s="9">
         <v>17076</v>
       </c>
-      <c r="F5" s="4" t="s">
+      <c r="F5" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="G5" s="6">
+      <c r="G5" s="12">
         <v>3070</v>
       </c>
-      <c r="H5" s="7">
-        <v>12</v>
-      </c>
-      <c r="I5" s="7" t="s">
+      <c r="H5" s="13">
+        <v>12</v>
+      </c>
+      <c r="I5" s="13" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A6" s="3">
+      <c r="A6" s="9">
         <v>1582</v>
       </c>
-      <c r="B6" s="3">
-        <v>162</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="D6" s="5">
+      <c r="B6" s="9">
+        <v>162</v>
+      </c>
+      <c r="C6" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="D6" s="11">
         <v>46233</v>
       </c>
-      <c r="E6" s="3">
+      <c r="E6" s="9">
         <v>7484</v>
       </c>
-      <c r="F6" s="4" t="s">
+      <c r="F6" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="G6" s="6">
+      <c r="G6" s="12">
         <v>9000</v>
       </c>
-      <c r="H6" s="7">
-        <v>12</v>
-      </c>
-      <c r="I6" s="7" t="s">
+      <c r="H6" s="13">
+        <v>12</v>
+      </c>
+      <c r="I6" s="13" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A7" s="3">
+      <c r="A7" s="9">
         <v>1582</v>
       </c>
-      <c r="B7" s="3">
-        <v>162</v>
-      </c>
-      <c r="C7" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="D7" s="5">
+      <c r="B7" s="9">
+        <v>162</v>
+      </c>
+      <c r="C7" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="D7" s="11">
         <v>46233</v>
       </c>
-      <c r="E7" s="3">
+      <c r="E7" s="9">
         <v>7485</v>
       </c>
-      <c r="F7" s="4" t="s">
+      <c r="F7" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="G7" s="6">
+      <c r="G7" s="12">
         <v>3000</v>
       </c>
-      <c r="H7" s="7">
-        <v>12</v>
-      </c>
-      <c r="I7" s="7" t="s">
+      <c r="H7" s="13">
+        <v>12</v>
+      </c>
+      <c r="I7" s="13" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A8" s="3">
+      <c r="A8" s="9">
         <v>1602</v>
       </c>
-      <c r="B8" s="3">
-        <v>162</v>
-      </c>
-      <c r="C8" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="D8" s="5">
+      <c r="B8" s="9">
+        <v>162</v>
+      </c>
+      <c r="C8" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="D8" s="11">
         <v>46239</v>
       </c>
-      <c r="E8" s="3">
+      <c r="E8" s="9">
         <v>7484</v>
       </c>
-      <c r="F8" s="4" t="s">
+      <c r="F8" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="G8" s="6">
+      <c r="G8" s="12">
         <v>10070</v>
       </c>
-      <c r="H8" s="7">
-        <v>12</v>
-      </c>
-      <c r="I8" s="7" t="s">
+      <c r="H8" s="13">
+        <v>12</v>
+      </c>
+      <c r="I8" s="13" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A9" s="3">
+      <c r="A9" s="9">
         <v>1633</v>
       </c>
-      <c r="B9" s="3">
-        <v>162</v>
-      </c>
-      <c r="C9" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="D9" s="5">
+      <c r="B9" s="9">
+        <v>162</v>
+      </c>
+      <c r="C9" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="D9" s="11">
         <v>46245</v>
       </c>
-      <c r="E9" s="3">
+      <c r="E9" s="9">
         <v>7485</v>
       </c>
-      <c r="F9" s="4" t="s">
+      <c r="F9" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="G9" s="6">
+      <c r="G9" s="12">
         <v>5000</v>
       </c>
-      <c r="H9" s="7">
-        <v>12</v>
-      </c>
-      <c r="I9" s="7" t="s">
+      <c r="H9" s="13">
+        <v>12</v>
+      </c>
+      <c r="I9" s="13" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A10" s="3">
+      <c r="A10" s="9">
         <v>1665</v>
       </c>
-      <c r="B10" s="3">
-        <v>162</v>
-      </c>
-      <c r="C10" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="D10" s="5">
+      <c r="B10" s="9">
+        <v>162</v>
+      </c>
+      <c r="C10" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="D10" s="11">
         <v>46252</v>
       </c>
-      <c r="E10" s="3">
+      <c r="E10" s="9">
+        <v>4413</v>
+      </c>
+      <c r="F10" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="G10" s="12">
+        <v>3000</v>
+      </c>
+      <c r="H10" s="13">
+        <v>12</v>
+      </c>
+      <c r="I10" s="13" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A11" s="9">
+        <v>1668</v>
+      </c>
+      <c r="B11" s="9">
+        <v>162</v>
+      </c>
+      <c r="C11" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="D11" s="11">
+        <v>46252</v>
+      </c>
+      <c r="E11" s="9">
+        <v>30189</v>
+      </c>
+      <c r="F11" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="G11" s="12">
+        <v>6500</v>
+      </c>
+      <c r="H11" s="13">
+        <v>12</v>
+      </c>
+      <c r="I11" s="13" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A12" s="14">
+        <v>1685</v>
+      </c>
+      <c r="B12" s="9">
+        <v>162</v>
+      </c>
+      <c r="C12" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="D12" s="11">
+        <v>46267</v>
+      </c>
+      <c r="E12" s="14">
+        <v>12514</v>
+      </c>
+      <c r="F12" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="G12" s="12">
+        <v>6000</v>
+      </c>
+      <c r="H12" s="13">
+        <v>12</v>
+      </c>
+      <c r="I12" s="13" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A13" s="14">
+        <v>1685</v>
+      </c>
+      <c r="B13" s="9">
+        <v>162</v>
+      </c>
+      <c r="C13" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="D13" s="11">
+        <v>46268</v>
+      </c>
+      <c r="E13" s="14">
+        <v>12515</v>
+      </c>
+      <c r="F13" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="G13" s="12">
+        <v>6700</v>
+      </c>
+      <c r="H13" s="13">
+        <v>12</v>
+      </c>
+      <c r="I13" s="13" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A14" s="14">
+        <v>1710</v>
+      </c>
+      <c r="B14" s="9">
+        <v>162</v>
+      </c>
+      <c r="C14" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="D14" s="11">
+        <v>46266</v>
+      </c>
+      <c r="E14" s="14">
+        <v>13150</v>
+      </c>
+      <c r="F14" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="G14" s="12">
+        <v>3000</v>
+      </c>
+      <c r="H14" s="13">
+        <v>12</v>
+      </c>
+      <c r="I14" s="13" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A15" s="14">
+        <v>1717</v>
+      </c>
+      <c r="B15" s="9">
+        <v>162</v>
+      </c>
+      <c r="C15" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="D15" s="11">
+        <v>46266</v>
+      </c>
+      <c r="E15" s="14">
+        <v>17075</v>
+      </c>
+      <c r="F15" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="G15" s="12">
+        <v>3000</v>
+      </c>
+      <c r="H15" s="13">
+        <v>12</v>
+      </c>
+      <c r="I15" s="13" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A16" s="14">
+        <v>1792</v>
+      </c>
+      <c r="B16" s="9">
+        <v>162</v>
+      </c>
+      <c r="C16" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="D16" s="11">
+        <v>46267</v>
+      </c>
+      <c r="E16" s="14">
         <v>7484</v>
       </c>
-      <c r="F10" s="4" t="s">
+      <c r="F16" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="G10" s="6">
-        <v>17300</v>
-      </c>
-      <c r="H10" s="7">
-        <v>12</v>
-      </c>
-      <c r="I10" s="7" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A11" s="3">
-        <v>1665</v>
-      </c>
-      <c r="B11" s="3">
-        <v>162</v>
-      </c>
-      <c r="C11" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="D11" s="5">
-        <v>46252</v>
-      </c>
-      <c r="E11" s="3">
-        <v>4413</v>
-      </c>
-      <c r="F11" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="G11" s="6">
-        <v>3000</v>
-      </c>
-      <c r="H11" s="7">
-        <v>12</v>
-      </c>
-      <c r="I11" s="7" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A12" s="3">
-        <v>1668</v>
-      </c>
-      <c r="B12" s="3">
-        <v>162</v>
-      </c>
-      <c r="C12" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="D12" s="5">
-        <v>46252</v>
-      </c>
-      <c r="E12" s="3">
-        <v>30189</v>
-      </c>
-      <c r="F12" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="G12" s="6">
-        <v>6500</v>
-      </c>
-      <c r="H12" s="7">
-        <v>12</v>
-      </c>
-      <c r="I12" s="7" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A13" s="8">
-        <v>1685</v>
-      </c>
-      <c r="B13" s="3">
-        <v>162</v>
-      </c>
-      <c r="C13" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="D13" s="5">
-        <v>46267</v>
-      </c>
-      <c r="E13" s="8">
-        <v>12514</v>
-      </c>
-      <c r="F13" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="G13" s="6">
-        <v>6000</v>
-      </c>
-      <c r="H13" s="7">
-        <v>12</v>
-      </c>
-      <c r="I13" s="7" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A14" s="8">
-        <v>1685</v>
-      </c>
-      <c r="B14" s="3">
-        <v>162</v>
-      </c>
-      <c r="C14" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="D14" s="5">
-        <v>46268</v>
-      </c>
-      <c r="E14" s="8">
-        <v>12515</v>
-      </c>
-      <c r="F14" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="G14" s="6">
-        <v>6700</v>
-      </c>
-      <c r="H14" s="7">
-        <v>12</v>
-      </c>
-      <c r="I14" s="7" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A15" s="8">
-        <v>1710</v>
-      </c>
-      <c r="B15" s="3">
-        <v>162</v>
-      </c>
-      <c r="C15" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="D15" s="5">
-        <v>46266</v>
-      </c>
-      <c r="E15" s="8">
-        <v>13150</v>
-      </c>
-      <c r="F15" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="G15" s="6">
-        <v>3000</v>
-      </c>
-      <c r="H15" s="7">
-        <v>12</v>
-      </c>
-      <c r="I15" s="7" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A16" s="8">
-        <v>1717</v>
-      </c>
-      <c r="B16" s="3">
-        <v>162</v>
-      </c>
-      <c r="C16" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="D16" s="5">
-        <v>46266</v>
-      </c>
-      <c r="E16" s="8">
-        <v>17075</v>
-      </c>
-      <c r="F16" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="G16" s="6">
-        <v>3000</v>
-      </c>
-      <c r="H16" s="7">
-        <v>12</v>
-      </c>
-      <c r="I16" s="7" t="s">
+      <c r="G16" s="12">
+        <v>20000</v>
+      </c>
+      <c r="H16" s="13">
+        <v>12</v>
+      </c>
+      <c r="I16" s="13" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A17" s="8">
-        <v>1792</v>
+        <v>1770</v>
       </c>
       <c r="B17" s="3">
         <v>162</v>
@@ -1043,16 +1055,16 @@
         <v>6</v>
       </c>
       <c r="D17" s="5">
-        <v>46267</v>
+        <v>46268</v>
       </c>
       <c r="E17" s="8">
-        <v>7484</v>
+        <v>9000</v>
       </c>
       <c r="F17" s="4" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="G17" s="6">
-        <v>20000</v>
+        <v>1000</v>
       </c>
       <c r="H17" s="7">
         <v>12</v>
@@ -1072,16 +1084,16 @@
         <v>6</v>
       </c>
       <c r="D18" s="5">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="E18" s="8">
-        <v>9000</v>
+        <v>10090</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="G18" s="6">
-        <v>1000</v>
+        <v>2000</v>
       </c>
       <c r="H18" s="7">
         <v>12</v>
@@ -1101,22 +1113,22 @@
         <v>6</v>
       </c>
       <c r="D19" s="5">
-        <v>46269</v>
+        <v>46270</v>
       </c>
       <c r="E19" s="8">
-        <v>10090</v>
+        <v>12517</v>
       </c>
       <c r="F19" s="4" t="s">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="G19" s="6">
-        <v>2000</v>
+        <v>1000</v>
       </c>
       <c r="H19" s="7">
         <v>12</v>
       </c>
       <c r="I19" s="7" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.3">
@@ -1130,10 +1142,10 @@
         <v>6</v>
       </c>
       <c r="D20" s="5">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="E20" s="8">
-        <v>12517</v>
+        <v>12518</v>
       </c>
       <c r="F20" s="4" t="s">
         <v>25</v>
@@ -1159,27 +1171,27 @@
         <v>6</v>
       </c>
       <c r="D21" s="5">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="E21" s="8">
-        <v>12518</v>
+        <v>17075</v>
       </c>
       <c r="F21" s="4" t="s">
-        <v>26</v>
+        <v>12</v>
       </c>
       <c r="G21" s="6">
-        <v>1000</v>
+        <v>2000</v>
       </c>
       <c r="H21" s="7">
         <v>12</v>
       </c>
       <c r="I21" s="7" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A22" s="8">
-        <v>1770</v>
+        <v>1840</v>
       </c>
       <c r="B22" s="3">
         <v>162</v>
@@ -1188,13 +1200,13 @@
         <v>6</v>
       </c>
       <c r="D22" s="5">
-        <v>46272</v>
+        <v>46288</v>
       </c>
       <c r="E22" s="8">
-        <v>17075</v>
+        <v>12517</v>
       </c>
       <c r="F22" s="4" t="s">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="G22" s="6">
         <v>2000</v>
@@ -1203,7 +1215,7 @@
         <v>12</v>
       </c>
       <c r="I22" s="7" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.3">
@@ -1220,7 +1232,7 @@
         <v>46288</v>
       </c>
       <c r="E23" s="8">
-        <v>12517</v>
+        <v>12518</v>
       </c>
       <c r="F23" s="4" t="s">
         <v>27</v>
@@ -1235,39 +1247,10 @@
         <v>18</v>
       </c>
     </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A24" s="8">
-        <v>1840</v>
-      </c>
-      <c r="B24" s="3">
-        <v>162</v>
-      </c>
-      <c r="C24" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="D24" s="5">
-        <v>46288</v>
-      </c>
-      <c r="E24" s="8">
-        <v>12518</v>
-      </c>
-      <c r="F24" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="G24" s="6">
-        <v>2000</v>
-      </c>
-      <c r="H24" s="7">
-        <v>12</v>
-      </c>
-      <c r="I24" s="7" t="s">
-        <v>18</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:I17" xr:uid="{00000000-0001-0000-0000-000000000000}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:I16">
-      <sortCondition ref="A1:A16"/>
+  <autoFilter ref="A1:I16" xr:uid="{00000000-0001-0000-0000-000000000000}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:I15">
+      <sortCondition ref="A1:A15"/>
     </sortState>
   </autoFilter>
   <printOptions gridLines="1"/>

--- a/data-source/COMPRATRANSFER.xlsx
+++ b/data-source/COMPRATRANSFER.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\impre\Downloads\TRANSFER-ANALISE-CORRIGIDO\data-source\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F0CEBF1E-428A-45CB-A3E8-FC1D812DEE91}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE78CEF0-728D-4F01-BFD9-0ABE05ED8E59}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Plan1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Plan1!$A$1:$I$16</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Plan1!$A$1:$I$12</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">Plan1!$1:$1</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="28">
   <si>
     <t>Núm.OC</t>
   </si>
@@ -76,9 +76,6 @@
   </si>
   <si>
     <t>QT-200A FULL TRANSFER - CAFÉ</t>
-  </si>
-  <si>
-    <t>QT-077A FULL TRANSFER - WHISKY</t>
   </si>
   <si>
     <t>Grupo</t>
@@ -148,6 +145,7 @@
       <sz val="11"/>
       <color rgb="FF800000"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="5">
@@ -566,7 +564,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I23"/>
+  <dimension ref="A1:I21"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.33203125" bestFit="1" customWidth="1"/>
@@ -600,18 +598,18 @@
         <v>5</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H1" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="I1" s="2" t="s">
         <v>14</v>
-      </c>
-      <c r="I1" s="2" t="s">
-        <v>15</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2" s="9">
-        <v>1565</v>
+        <v>1582</v>
       </c>
       <c r="B2" s="9">
         <v>162</v>
@@ -620,7 +618,7 @@
         <v>6</v>
       </c>
       <c r="D2" s="11">
-        <v>46225</v>
+        <v>46233</v>
       </c>
       <c r="E2" s="9">
         <v>7484</v>
@@ -629,18 +627,18 @@
         <v>9</v>
       </c>
       <c r="G2" s="12">
-        <v>8800</v>
+        <v>9000</v>
       </c>
       <c r="H2" s="13">
         <v>12</v>
       </c>
       <c r="I2" s="13" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A3" s="9">
-        <v>1565</v>
+        <v>1582</v>
       </c>
       <c r="B3" s="9">
         <v>162</v>
@@ -649,7 +647,7 @@
         <v>6</v>
       </c>
       <c r="D3" s="11">
-        <v>46225</v>
+        <v>46233</v>
       </c>
       <c r="E3" s="9">
         <v>7485</v>
@@ -658,18 +656,18 @@
         <v>7</v>
       </c>
       <c r="G3" s="12">
-        <v>6000</v>
+        <v>3000</v>
       </c>
       <c r="H3" s="13">
         <v>12</v>
       </c>
       <c r="I3" s="13" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A4" s="9">
-        <v>1565</v>
+        <v>1602</v>
       </c>
       <c r="B4" s="9">
         <v>162</v>
@@ -678,27 +676,27 @@
         <v>6</v>
       </c>
       <c r="D4" s="11">
-        <v>46225</v>
+        <v>46239</v>
       </c>
       <c r="E4" s="9">
-        <v>10090</v>
+        <v>7484</v>
       </c>
       <c r="F4" s="10" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G4" s="12">
-        <v>3200</v>
+        <v>10070</v>
       </c>
       <c r="H4" s="13">
         <v>12</v>
       </c>
       <c r="I4" s="13" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A5" s="9">
-        <v>1565</v>
+        <v>1633</v>
       </c>
       <c r="B5" s="9">
         <v>162</v>
@@ -707,27 +705,27 @@
         <v>6</v>
       </c>
       <c r="D5" s="11">
-        <v>46225</v>
+        <v>46245</v>
       </c>
       <c r="E5" s="9">
-        <v>17076</v>
+        <v>7485</v>
       </c>
       <c r="F5" s="10" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="G5" s="12">
-        <v>3070</v>
+        <v>5000</v>
       </c>
       <c r="H5" s="13">
         <v>12</v>
       </c>
       <c r="I5" s="13" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A6" s="9">
-        <v>1582</v>
+        <v>1665</v>
       </c>
       <c r="B6" s="9">
         <v>162</v>
@@ -736,27 +734,27 @@
         <v>6</v>
       </c>
       <c r="D6" s="11">
-        <v>46233</v>
+        <v>46252</v>
       </c>
       <c r="E6" s="9">
-        <v>7484</v>
+        <v>4413</v>
       </c>
       <c r="F6" s="10" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G6" s="12">
-        <v>9000</v>
+        <v>3000</v>
       </c>
       <c r="H6" s="13">
         <v>12</v>
       </c>
       <c r="I6" s="13" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A7" s="9">
-        <v>1582</v>
+        <v>1668</v>
       </c>
       <c r="B7" s="9">
         <v>162</v>
@@ -765,27 +763,27 @@
         <v>6</v>
       </c>
       <c r="D7" s="11">
-        <v>46233</v>
+        <v>46252</v>
       </c>
       <c r="E7" s="9">
-        <v>7485</v>
+        <v>30189</v>
       </c>
       <c r="F7" s="10" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="G7" s="12">
-        <v>3000</v>
+        <v>6500</v>
       </c>
       <c r="H7" s="13">
         <v>12</v>
       </c>
       <c r="I7" s="13" t="s">
-        <v>17</v>
+        <v>27</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A8" s="9">
-        <v>1602</v>
+      <c r="A8" s="14">
+        <v>1685</v>
       </c>
       <c r="B8" s="9">
         <v>162</v>
@@ -794,16 +792,16 @@
         <v>6</v>
       </c>
       <c r="D8" s="11">
-        <v>46239</v>
-      </c>
-      <c r="E8" s="9">
-        <v>7484</v>
+        <v>46267</v>
+      </c>
+      <c r="E8" s="14">
+        <v>12514</v>
       </c>
       <c r="F8" s="10" t="s">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="G8" s="12">
-        <v>10070</v>
+        <v>6000</v>
       </c>
       <c r="H8" s="13">
         <v>12</v>
@@ -813,8 +811,8 @@
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A9" s="9">
-        <v>1633</v>
+      <c r="A9" s="14">
+        <v>1685</v>
       </c>
       <c r="B9" s="9">
         <v>162</v>
@@ -823,16 +821,16 @@
         <v>6</v>
       </c>
       <c r="D9" s="11">
-        <v>46245</v>
-      </c>
-      <c r="E9" s="9">
-        <v>7485</v>
+        <v>46268</v>
+      </c>
+      <c r="E9" s="14">
+        <v>12515</v>
       </c>
       <c r="F9" s="10" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="G9" s="12">
-        <v>5000</v>
+        <v>6700</v>
       </c>
       <c r="H9" s="13">
         <v>12</v>
@@ -842,8 +840,8 @@
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A10" s="9">
-        <v>1665</v>
+      <c r="A10" s="14">
+        <v>1710</v>
       </c>
       <c r="B10" s="9">
         <v>162</v>
@@ -852,56 +850,56 @@
         <v>6</v>
       </c>
       <c r="D10" s="11">
-        <v>46252</v>
-      </c>
-      <c r="E10" s="9">
-        <v>4413</v>
+        <v>46266</v>
+      </c>
+      <c r="E10" s="14">
+        <v>13150</v>
       </c>
       <c r="F10" s="10" t="s">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="G10" s="12">
-        <v>3000</v>
+        <v>3580</v>
       </c>
       <c r="H10" s="13">
         <v>12</v>
       </c>
       <c r="I10" s="13" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A11" s="14">
+        <v>1717</v>
+      </c>
+      <c r="B11" s="9">
+        <v>162</v>
+      </c>
+      <c r="C11" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="D11" s="11">
+        <v>46266</v>
+      </c>
+      <c r="E11" s="14">
+        <v>17075</v>
+      </c>
+      <c r="F11" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="G11" s="12">
+        <v>3130</v>
+      </c>
+      <c r="H11" s="13">
+        <v>12</v>
+      </c>
+      <c r="I11" s="13" t="s">
         <v>16</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A11" s="9">
-        <v>1668</v>
-      </c>
-      <c r="B11" s="9">
-        <v>162</v>
-      </c>
-      <c r="C11" s="10" t="s">
-        <v>6</v>
-      </c>
-      <c r="D11" s="11">
-        <v>46252</v>
-      </c>
-      <c r="E11" s="9">
-        <v>30189</v>
-      </c>
-      <c r="F11" s="10" t="s">
-        <v>20</v>
-      </c>
-      <c r="G11" s="12">
-        <v>6500</v>
-      </c>
-      <c r="H11" s="13">
-        <v>12</v>
-      </c>
-      <c r="I11" s="13" t="s">
-        <v>28</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A12" s="14">
-        <v>1685</v>
+        <v>1792</v>
       </c>
       <c r="B12" s="9">
         <v>162</v>
@@ -913,134 +911,134 @@
         <v>46267</v>
       </c>
       <c r="E12" s="14">
-        <v>12514</v>
+        <v>7484</v>
       </c>
       <c r="F12" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="G12" s="12">
+        <v>20000</v>
+      </c>
+      <c r="H12" s="13">
+        <v>12</v>
+      </c>
+      <c r="I12" s="13" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A13" s="8">
+        <v>1770</v>
+      </c>
+      <c r="B13" s="3">
+        <v>162</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D13" s="5">
+        <v>46268</v>
+      </c>
+      <c r="E13" s="8">
+        <v>9000</v>
+      </c>
+      <c r="F13" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="G13" s="6">
+        <v>1080</v>
+      </c>
+      <c r="H13" s="7">
+        <v>12</v>
+      </c>
+      <c r="I13" s="7" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A14" s="8">
+        <v>1770</v>
+      </c>
+      <c r="B14" s="3">
+        <v>162</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D14" s="5">
+        <v>46269</v>
+      </c>
+      <c r="E14" s="8">
+        <v>10090</v>
+      </c>
+      <c r="F14" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G14" s="6">
+        <v>2200</v>
+      </c>
+      <c r="H14" s="7">
+        <v>12</v>
+      </c>
+      <c r="I14" s="7" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A15" s="8">
+        <v>1770</v>
+      </c>
+      <c r="B15" s="3">
+        <v>162</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D15" s="5">
+        <v>46270</v>
+      </c>
+      <c r="E15" s="8">
+        <v>12517</v>
+      </c>
+      <c r="F15" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="G12" s="12">
-        <v>6000</v>
-      </c>
-      <c r="H12" s="13">
-        <v>12</v>
-      </c>
-      <c r="I12" s="13" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A13" s="14">
-        <v>1685</v>
-      </c>
-      <c r="B13" s="9">
-        <v>162</v>
-      </c>
-      <c r="C13" s="10" t="s">
-        <v>6</v>
-      </c>
-      <c r="D13" s="11">
-        <v>46268</v>
-      </c>
-      <c r="E13" s="14">
-        <v>12515</v>
-      </c>
-      <c r="F13" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="G13" s="12">
-        <v>6700</v>
-      </c>
-      <c r="H13" s="13">
-        <v>12</v>
-      </c>
-      <c r="I13" s="13" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A14" s="14">
-        <v>1710</v>
-      </c>
-      <c r="B14" s="9">
-        <v>162</v>
-      </c>
-      <c r="C14" s="10" t="s">
-        <v>6</v>
-      </c>
-      <c r="D14" s="11">
-        <v>46266</v>
-      </c>
-      <c r="E14" s="14">
-        <v>13150</v>
-      </c>
-      <c r="F14" s="10" t="s">
-        <v>22</v>
-      </c>
-      <c r="G14" s="12">
-        <v>3000</v>
-      </c>
-      <c r="H14" s="13">
-        <v>12</v>
-      </c>
-      <c r="I14" s="13" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A15" s="14">
-        <v>1717</v>
-      </c>
-      <c r="B15" s="9">
-        <v>162</v>
-      </c>
-      <c r="C15" s="10" t="s">
-        <v>6</v>
-      </c>
-      <c r="D15" s="11">
-        <v>46266</v>
-      </c>
-      <c r="E15" s="14">
-        <v>17075</v>
-      </c>
-      <c r="F15" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="G15" s="12">
-        <v>3000</v>
-      </c>
-      <c r="H15" s="13">
-        <v>12</v>
-      </c>
-      <c r="I15" s="13" t="s">
+      <c r="G15" s="6">
+        <v>700</v>
+      </c>
+      <c r="H15" s="7">
+        <v>12</v>
+      </c>
+      <c r="I15" s="7" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A16" s="14">
-        <v>1792</v>
-      </c>
-      <c r="B16" s="9">
-        <v>162</v>
-      </c>
-      <c r="C16" s="10" t="s">
-        <v>6</v>
-      </c>
-      <c r="D16" s="11">
-        <v>46267</v>
-      </c>
-      <c r="E16" s="14">
-        <v>7484</v>
-      </c>
-      <c r="F16" s="10" t="s">
-        <v>9</v>
-      </c>
-      <c r="G16" s="12">
-        <v>20000</v>
-      </c>
-      <c r="H16" s="13">
-        <v>12</v>
-      </c>
-      <c r="I16" s="13" t="s">
+      <c r="A16" s="8">
+        <v>1770</v>
+      </c>
+      <c r="B16" s="3">
+        <v>162</v>
+      </c>
+      <c r="C16" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D16" s="5">
+        <v>46271</v>
+      </c>
+      <c r="E16" s="8">
+        <v>12518</v>
+      </c>
+      <c r="F16" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="G16" s="6">
+        <v>1000</v>
+      </c>
+      <c r="H16" s="7">
+        <v>12</v>
+      </c>
+      <c r="I16" s="7" t="s">
         <v>17</v>
       </c>
     </row>
@@ -1055,27 +1053,27 @@
         <v>6</v>
       </c>
       <c r="D17" s="5">
-        <v>46268</v>
+        <v>46272</v>
       </c>
       <c r="E17" s="8">
-        <v>9000</v>
+        <v>17075</v>
       </c>
       <c r="F17" s="4" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="G17" s="6">
-        <v>1000</v>
+        <v>2200</v>
       </c>
       <c r="H17" s="7">
         <v>12</v>
       </c>
       <c r="I17" s="7" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A18" s="8">
-        <v>1770</v>
+        <v>1840</v>
       </c>
       <c r="B18" s="3">
         <v>162</v>
@@ -1084,13 +1082,13 @@
         <v>6</v>
       </c>
       <c r="D18" s="5">
-        <v>46269</v>
+        <v>46288</v>
       </c>
       <c r="E18" s="8">
-        <v>10090</v>
+        <v>12517</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="G18" s="6">
         <v>2000</v>
@@ -1104,7 +1102,7 @@
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A19" s="8">
-        <v>1770</v>
+        <v>1840</v>
       </c>
       <c r="B19" s="3">
         <v>162</v>
@@ -1113,144 +1111,86 @@
         <v>6</v>
       </c>
       <c r="D19" s="5">
-        <v>46270</v>
+        <v>46288</v>
       </c>
       <c r="E19" s="8">
-        <v>12517</v>
+        <v>12518</v>
       </c>
       <c r="F19" s="4" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="G19" s="6">
-        <v>1000</v>
+        <v>2000</v>
       </c>
       <c r="H19" s="7">
         <v>12</v>
       </c>
       <c r="I19" s="7" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A20" s="8">
-        <v>1770</v>
+        <v>1942</v>
       </c>
       <c r="B20" s="3">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="C20" s="4" t="s">
         <v>6</v>
       </c>
       <c r="D20" s="5">
-        <v>46271</v>
-      </c>
-      <c r="E20" s="8">
-        <v>12518</v>
-      </c>
-      <c r="F20" s="4" t="s">
-        <v>25</v>
+        <v>46308</v>
+      </c>
+      <c r="E20" s="9">
+        <v>7485</v>
+      </c>
+      <c r="F20" s="10" t="s">
+        <v>7</v>
       </c>
       <c r="G20" s="6">
-        <v>1000</v>
+        <v>6000</v>
       </c>
       <c r="H20" s="7">
         <v>12</v>
       </c>
       <c r="I20" s="7" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A21" s="8">
-        <v>1770</v>
+        <v>1942</v>
       </c>
       <c r="B21" s="3">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="C21" s="4" t="s">
         <v>6</v>
       </c>
       <c r="D21" s="5">
-        <v>46272</v>
+        <v>46308</v>
       </c>
       <c r="E21" s="8">
-        <v>17075</v>
+        <v>9000</v>
       </c>
       <c r="F21" s="4" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="G21" s="6">
-        <v>2000</v>
+        <v>1000</v>
       </c>
       <c r="H21" s="7">
         <v>12</v>
       </c>
       <c r="I21" s="7" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A22" s="8">
-        <v>1840</v>
-      </c>
-      <c r="B22" s="3">
-        <v>162</v>
-      </c>
-      <c r="C22" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="D22" s="5">
-        <v>46288</v>
-      </c>
-      <c r="E22" s="8">
-        <v>12517</v>
-      </c>
-      <c r="F22" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="G22" s="6">
-        <v>2000</v>
-      </c>
-      <c r="H22" s="7">
-        <v>12</v>
-      </c>
-      <c r="I22" s="7" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A23" s="8">
-        <v>1840</v>
-      </c>
-      <c r="B23" s="3">
-        <v>162</v>
-      </c>
-      <c r="C23" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="D23" s="5">
-        <v>46288</v>
-      </c>
-      <c r="E23" s="8">
-        <v>12518</v>
-      </c>
-      <c r="F23" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="G23" s="6">
-        <v>2000</v>
-      </c>
-      <c r="H23" s="7">
-        <v>12</v>
-      </c>
-      <c r="I23" s="7" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I16" xr:uid="{00000000-0001-0000-0000-000000000000}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:I15">
-      <sortCondition ref="A1:A15"/>
+  <autoFilter ref="A1:I12" xr:uid="{00000000-0001-0000-0000-000000000000}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:I11">
+      <sortCondition ref="A1:A11"/>
     </sortState>
   </autoFilter>
   <printOptions gridLines="1"/>

--- a/data-source/COMPRATRANSFER.xlsx
+++ b/data-source/COMPRATRANSFER.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30527"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\impre\Downloads\TRANSFER-ANALISE-CORRIGIDO\data-source\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE78CEF0-728D-4F01-BFD9-0ABE05ED8E59}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{25904AD9-7DB0-4089-8A81-7ABC4BC28CF7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Plan1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Plan1!$A$1:$I$12</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Plan1!$A$1:$I$11</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">Plan1!$1:$1</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="30">
   <si>
     <t>Núm.OC</t>
   </si>
@@ -121,6 +121,12 @@
   </si>
   <si>
     <t>PROTECTION</t>
+  </si>
+  <si>
+    <t>TRANSF PARC FURTA COR 201 - MOD 99-5 AM</t>
+  </si>
+  <si>
+    <t>FURTACOR</t>
   </si>
 </sst>
 </file>
@@ -148,7 +154,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -169,6 +175,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="3" tint="0.89999084444715716"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.39997558519241921"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -211,7 +223,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -227,6 +239,12 @@
     <xf numFmtId="165" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="166" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="49" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="14" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="165" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="166" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -608,269 +626,269 @@
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A2" s="9">
+      <c r="A2" s="15">
         <v>1582</v>
       </c>
-      <c r="B2" s="9">
-        <v>162</v>
-      </c>
-      <c r="C2" s="10" t="s">
-        <v>6</v>
-      </c>
-      <c r="D2" s="11">
+      <c r="B2" s="15">
+        <v>162</v>
+      </c>
+      <c r="C2" s="16" t="s">
+        <v>6</v>
+      </c>
+      <c r="D2" s="17">
         <v>46233</v>
       </c>
-      <c r="E2" s="9">
+      <c r="E2" s="15">
         <v>7484</v>
       </c>
-      <c r="F2" s="10" t="s">
+      <c r="F2" s="16" t="s">
         <v>9</v>
       </c>
-      <c r="G2" s="12">
+      <c r="G2" s="18">
         <v>9000</v>
       </c>
-      <c r="H2" s="13">
-        <v>12</v>
-      </c>
-      <c r="I2" s="13" t="s">
+      <c r="H2" s="19">
+        <v>12</v>
+      </c>
+      <c r="I2" s="19" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A3" s="9">
+      <c r="A3" s="15">
         <v>1582</v>
       </c>
-      <c r="B3" s="9">
-        <v>162</v>
-      </c>
-      <c r="C3" s="10" t="s">
-        <v>6</v>
-      </c>
-      <c r="D3" s="11">
+      <c r="B3" s="15">
+        <v>162</v>
+      </c>
+      <c r="C3" s="16" t="s">
+        <v>6</v>
+      </c>
+      <c r="D3" s="17">
         <v>46233</v>
       </c>
-      <c r="E3" s="9">
+      <c r="E3" s="15">
         <v>7485</v>
       </c>
-      <c r="F3" s="10" t="s">
+      <c r="F3" s="16" t="s">
         <v>7</v>
       </c>
-      <c r="G3" s="12">
+      <c r="G3" s="18">
         <v>3000</v>
       </c>
-      <c r="H3" s="13">
-        <v>12</v>
-      </c>
-      <c r="I3" s="13" t="s">
+      <c r="H3" s="19">
+        <v>12</v>
+      </c>
+      <c r="I3" s="19" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A4" s="9">
+      <c r="A4" s="15">
         <v>1602</v>
       </c>
-      <c r="B4" s="9">
-        <v>162</v>
-      </c>
-      <c r="C4" s="10" t="s">
-        <v>6</v>
-      </c>
-      <c r="D4" s="11">
+      <c r="B4" s="15">
+        <v>162</v>
+      </c>
+      <c r="C4" s="16" t="s">
+        <v>6</v>
+      </c>
+      <c r="D4" s="17">
         <v>46239</v>
       </c>
-      <c r="E4" s="9">
+      <c r="E4" s="15">
         <v>7484</v>
       </c>
-      <c r="F4" s="10" t="s">
+      <c r="F4" s="16" t="s">
         <v>9</v>
       </c>
-      <c r="G4" s="12">
+      <c r="G4" s="18">
         <v>10070</v>
       </c>
-      <c r="H4" s="13">
-        <v>12</v>
-      </c>
-      <c r="I4" s="13" t="s">
+      <c r="H4" s="19">
+        <v>12</v>
+      </c>
+      <c r="I4" s="19" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A5" s="9">
-        <v>1633</v>
-      </c>
-      <c r="B5" s="9">
-        <v>162</v>
-      </c>
-      <c r="C5" s="10" t="s">
-        <v>6</v>
-      </c>
-      <c r="D5" s="11">
-        <v>46245</v>
-      </c>
-      <c r="E5" s="9">
-        <v>7485</v>
-      </c>
-      <c r="F5" s="10" t="s">
-        <v>7</v>
-      </c>
-      <c r="G5" s="12">
-        <v>5000</v>
-      </c>
-      <c r="H5" s="13">
-        <v>12</v>
-      </c>
-      <c r="I5" s="13" t="s">
+      <c r="A5" s="15">
+        <v>1665</v>
+      </c>
+      <c r="B5" s="15">
+        <v>162</v>
+      </c>
+      <c r="C5" s="16" t="s">
+        <v>6</v>
+      </c>
+      <c r="D5" s="17">
+        <v>46252</v>
+      </c>
+      <c r="E5" s="15">
+        <v>4413</v>
+      </c>
+      <c r="F5" s="16" t="s">
+        <v>8</v>
+      </c>
+      <c r="G5" s="18">
+        <v>3000</v>
+      </c>
+      <c r="H5" s="19">
+        <v>12</v>
+      </c>
+      <c r="I5" s="19" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A6" s="15">
+        <v>1668</v>
+      </c>
+      <c r="B6" s="15">
+        <v>162</v>
+      </c>
+      <c r="C6" s="16" t="s">
+        <v>6</v>
+      </c>
+      <c r="D6" s="17">
+        <v>46252</v>
+      </c>
+      <c r="E6" s="15">
+        <v>30189</v>
+      </c>
+      <c r="F6" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="G6" s="18">
+        <v>6500</v>
+      </c>
+      <c r="H6" s="19">
+        <v>12</v>
+      </c>
+      <c r="I6" s="19" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A7" s="20">
+        <v>1685</v>
+      </c>
+      <c r="B7" s="15">
+        <v>162</v>
+      </c>
+      <c r="C7" s="16" t="s">
+        <v>6</v>
+      </c>
+      <c r="D7" s="17">
+        <v>46267</v>
+      </c>
+      <c r="E7" s="20">
+        <v>12514</v>
+      </c>
+      <c r="F7" s="16" t="s">
+        <v>22</v>
+      </c>
+      <c r="G7" s="18">
+        <v>6000</v>
+      </c>
+      <c r="H7" s="19">
+        <v>12</v>
+      </c>
+      <c r="I7" s="19" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A8" s="20">
+        <v>1685</v>
+      </c>
+      <c r="B8" s="15">
+        <v>162</v>
+      </c>
+      <c r="C8" s="16" t="s">
+        <v>6</v>
+      </c>
+      <c r="D8" s="17">
+        <v>46268</v>
+      </c>
+      <c r="E8" s="20">
+        <v>12515</v>
+      </c>
+      <c r="F8" s="16" t="s">
+        <v>11</v>
+      </c>
+      <c r="G8" s="18">
+        <v>6700</v>
+      </c>
+      <c r="H8" s="19">
+        <v>12</v>
+      </c>
+      <c r="I8" s="19" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A9" s="20">
+        <v>1710</v>
+      </c>
+      <c r="B9" s="15">
+        <v>162</v>
+      </c>
+      <c r="C9" s="16" t="s">
+        <v>6</v>
+      </c>
+      <c r="D9" s="17">
+        <v>46266</v>
+      </c>
+      <c r="E9" s="20">
+        <v>13150</v>
+      </c>
+      <c r="F9" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="G9" s="18">
+        <v>3580</v>
+      </c>
+      <c r="H9" s="19">
+        <v>12</v>
+      </c>
+      <c r="I9" s="19" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A10" s="20">
+        <v>1717</v>
+      </c>
+      <c r="B10" s="15">
+        <v>162</v>
+      </c>
+      <c r="C10" s="16" t="s">
+        <v>6</v>
+      </c>
+      <c r="D10" s="17">
+        <v>46266</v>
+      </c>
+      <c r="E10" s="20">
+        <v>17075</v>
+      </c>
+      <c r="F10" s="16" t="s">
+        <v>12</v>
+      </c>
+      <c r="G10" s="18">
+        <v>3130</v>
+      </c>
+      <c r="H10" s="19">
+        <v>12</v>
+      </c>
+      <c r="I10" s="19" t="s">
         <v>16</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A6" s="9">
-        <v>1665</v>
-      </c>
-      <c r="B6" s="9">
-        <v>162</v>
-      </c>
-      <c r="C6" s="10" t="s">
-        <v>6</v>
-      </c>
-      <c r="D6" s="11">
-        <v>46252</v>
-      </c>
-      <c r="E6" s="9">
-        <v>4413</v>
-      </c>
-      <c r="F6" s="10" t="s">
-        <v>8</v>
-      </c>
-      <c r="G6" s="12">
-        <v>3000</v>
-      </c>
-      <c r="H6" s="13">
-        <v>12</v>
-      </c>
-      <c r="I6" s="13" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A7" s="9">
-        <v>1668</v>
-      </c>
-      <c r="B7" s="9">
-        <v>162</v>
-      </c>
-      <c r="C7" s="10" t="s">
-        <v>6</v>
-      </c>
-      <c r="D7" s="11">
-        <v>46252</v>
-      </c>
-      <c r="E7" s="9">
-        <v>30189</v>
-      </c>
-      <c r="F7" s="10" t="s">
-        <v>19</v>
-      </c>
-      <c r="G7" s="12">
-        <v>6500</v>
-      </c>
-      <c r="H7" s="13">
-        <v>12</v>
-      </c>
-      <c r="I7" s="13" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A8" s="14">
-        <v>1685</v>
-      </c>
-      <c r="B8" s="9">
-        <v>162</v>
-      </c>
-      <c r="C8" s="10" t="s">
-        <v>6</v>
-      </c>
-      <c r="D8" s="11">
-        <v>46267</v>
-      </c>
-      <c r="E8" s="14">
-        <v>12514</v>
-      </c>
-      <c r="F8" s="10" t="s">
-        <v>22</v>
-      </c>
-      <c r="G8" s="12">
-        <v>6000</v>
-      </c>
-      <c r="H8" s="13">
-        <v>12</v>
-      </c>
-      <c r="I8" s="13" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A9" s="14">
-        <v>1685</v>
-      </c>
-      <c r="B9" s="9">
-        <v>162</v>
-      </c>
-      <c r="C9" s="10" t="s">
-        <v>6</v>
-      </c>
-      <c r="D9" s="11">
-        <v>46268</v>
-      </c>
-      <c r="E9" s="14">
-        <v>12515</v>
-      </c>
-      <c r="F9" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="G9" s="12">
-        <v>6700</v>
-      </c>
-      <c r="H9" s="13">
-        <v>12</v>
-      </c>
-      <c r="I9" s="13" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A10" s="14">
-        <v>1710</v>
-      </c>
-      <c r="B10" s="9">
-        <v>162</v>
-      </c>
-      <c r="C10" s="10" t="s">
-        <v>6</v>
-      </c>
-      <c r="D10" s="11">
-        <v>46266</v>
-      </c>
-      <c r="E10" s="14">
-        <v>13150</v>
-      </c>
-      <c r="F10" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="G10" s="12">
-        <v>3580</v>
-      </c>
-      <c r="H10" s="13">
-        <v>12</v>
-      </c>
-      <c r="I10" s="13" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A11" s="14">
-        <v>1717</v>
+        <v>1792</v>
       </c>
       <c r="B11" s="9">
         <v>162</v>
@@ -879,16 +897,16 @@
         <v>6</v>
       </c>
       <c r="D11" s="11">
-        <v>46266</v>
+        <v>46267</v>
       </c>
       <c r="E11" s="14">
-        <v>17075</v>
+        <v>7484</v>
       </c>
       <c r="F11" s="10" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="G11" s="12">
-        <v>3130</v>
+        <v>20000</v>
       </c>
       <c r="H11" s="13">
         <v>12</v>
@@ -898,31 +916,31 @@
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A12" s="14">
-        <v>1792</v>
-      </c>
-      <c r="B12" s="9">
-        <v>162</v>
-      </c>
-      <c r="C12" s="10" t="s">
-        <v>6</v>
-      </c>
-      <c r="D12" s="11">
-        <v>46267</v>
-      </c>
-      <c r="E12" s="14">
-        <v>7484</v>
-      </c>
-      <c r="F12" s="10" t="s">
-        <v>9</v>
-      </c>
-      <c r="G12" s="12">
-        <v>20000</v>
-      </c>
-      <c r="H12" s="13">
-        <v>12</v>
-      </c>
-      <c r="I12" s="13" t="s">
+      <c r="A12" s="8">
+        <v>1770</v>
+      </c>
+      <c r="B12" s="3">
+        <v>162</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D12" s="5">
+        <v>46268</v>
+      </c>
+      <c r="E12" s="8">
+        <v>9000</v>
+      </c>
+      <c r="F12" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="G12" s="6">
+        <v>1080</v>
+      </c>
+      <c r="H12" s="7">
+        <v>12</v>
+      </c>
+      <c r="I12" s="7" t="s">
         <v>16</v>
       </c>
     </row>
@@ -937,16 +955,16 @@
         <v>6</v>
       </c>
       <c r="D13" s="5">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="E13" s="8">
-        <v>9000</v>
+        <v>10090</v>
       </c>
       <c r="F13" s="4" t="s">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="G13" s="6">
-        <v>1080</v>
+        <v>2200</v>
       </c>
       <c r="H13" s="7">
         <v>12</v>
@@ -966,22 +984,22 @@
         <v>6</v>
       </c>
       <c r="D14" s="5">
-        <v>46269</v>
+        <v>46270</v>
       </c>
       <c r="E14" s="8">
-        <v>10090</v>
+        <v>12517</v>
       </c>
       <c r="F14" s="4" t="s">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="G14" s="6">
-        <v>2200</v>
+        <v>700</v>
       </c>
       <c r="H14" s="7">
         <v>12</v>
       </c>
       <c r="I14" s="7" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.3">
@@ -995,16 +1013,16 @@
         <v>6</v>
       </c>
       <c r="D15" s="5">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="E15" s="8">
-        <v>12517</v>
+        <v>12518</v>
       </c>
       <c r="F15" s="4" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G15" s="6">
-        <v>700</v>
+        <v>1000</v>
       </c>
       <c r="H15" s="7">
         <v>12</v>
@@ -1024,27 +1042,27 @@
         <v>6</v>
       </c>
       <c r="D16" s="5">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="E16" s="8">
-        <v>12518</v>
+        <v>17075</v>
       </c>
       <c r="F16" s="4" t="s">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="G16" s="6">
-        <v>1000</v>
+        <v>2200</v>
       </c>
       <c r="H16" s="7">
         <v>12</v>
       </c>
       <c r="I16" s="7" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A17" s="8">
-        <v>1770</v>
+        <v>1840</v>
       </c>
       <c r="B17" s="3">
         <v>162</v>
@@ -1053,22 +1071,22 @@
         <v>6</v>
       </c>
       <c r="D17" s="5">
-        <v>46272</v>
+        <v>46288</v>
       </c>
       <c r="E17" s="8">
-        <v>17075</v>
+        <v>12517</v>
       </c>
       <c r="F17" s="4" t="s">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="G17" s="6">
-        <v>2200</v>
+        <v>2000</v>
       </c>
       <c r="H17" s="7">
         <v>12</v>
       </c>
       <c r="I17" s="7" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.3">
@@ -1085,10 +1103,10 @@
         <v>46288</v>
       </c>
       <c r="E18" s="8">
-        <v>12517</v>
+        <v>12518</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G18" s="6">
         <v>2000</v>
@@ -1102,7 +1120,7 @@
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A19" s="8">
-        <v>1840</v>
+        <v>1942</v>
       </c>
       <c r="B19" s="3">
         <v>162</v>
@@ -1111,22 +1129,22 @@
         <v>6</v>
       </c>
       <c r="D19" s="5">
-        <v>46288</v>
-      </c>
-      <c r="E19" s="8">
-        <v>12518</v>
-      </c>
-      <c r="F19" s="4" t="s">
-        <v>26</v>
+        <v>46308</v>
+      </c>
+      <c r="E19" s="9">
+        <v>7485</v>
+      </c>
+      <c r="F19" s="10" t="s">
+        <v>7</v>
       </c>
       <c r="G19" s="6">
-        <v>2000</v>
+        <v>6000</v>
       </c>
       <c r="H19" s="7">
         <v>12</v>
       </c>
       <c r="I19" s="7" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.3">
@@ -1134,7 +1152,7 @@
         <v>1942</v>
       </c>
       <c r="B20" s="3">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C20" s="4" t="s">
         <v>6</v>
@@ -1142,14 +1160,14 @@
       <c r="D20" s="5">
         <v>46308</v>
       </c>
-      <c r="E20" s="9">
-        <v>7485</v>
-      </c>
-      <c r="F20" s="10" t="s">
-        <v>7</v>
+      <c r="E20" s="8">
+        <v>9000</v>
+      </c>
+      <c r="F20" s="4" t="s">
+        <v>20</v>
       </c>
       <c r="G20" s="6">
-        <v>6000</v>
+        <v>2000</v>
       </c>
       <c r="H20" s="7">
         <v>12</v>
@@ -1159,38 +1177,38 @@
       </c>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A21" s="8">
-        <v>1942</v>
-      </c>
-      <c r="B21" s="3">
-        <v>164</v>
-      </c>
-      <c r="C21" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="D21" s="5">
-        <v>46308</v>
-      </c>
-      <c r="E21" s="8">
-        <v>9000</v>
-      </c>
-      <c r="F21" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="G21" s="6">
-        <v>1000</v>
-      </c>
-      <c r="H21" s="7">
-        <v>12</v>
-      </c>
-      <c r="I21" s="7" t="s">
-        <v>16</v>
+      <c r="A21" s="19">
+        <v>1971</v>
+      </c>
+      <c r="B21" s="15">
+        <v>162</v>
+      </c>
+      <c r="C21" s="16" t="s">
+        <v>6</v>
+      </c>
+      <c r="D21" s="17">
+        <v>46314</v>
+      </c>
+      <c r="E21" s="19">
+        <v>27</v>
+      </c>
+      <c r="F21" s="19" t="s">
+        <v>28</v>
+      </c>
+      <c r="G21" s="18">
+        <v>5000</v>
+      </c>
+      <c r="H21" s="19">
+        <v>12</v>
+      </c>
+      <c r="I21" s="19" t="s">
+        <v>29</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I12" xr:uid="{00000000-0001-0000-0000-000000000000}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:I11">
-      <sortCondition ref="A1:A11"/>
+  <autoFilter ref="A1:I11" xr:uid="{00000000-0001-0000-0000-000000000000}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:I10">
+      <sortCondition ref="A1:A10"/>
     </sortState>
   </autoFilter>
   <printOptions gridLines="1"/>
